--- a/patient_feedback_forms/028_post_surgery_physiotherapy_evaluation_form--patient_feedback_forms.xlsx
+++ b/patient_feedback_forms/028_post_surgery_physiotherapy_evaluation_form--patient_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'head',_'label':_'head',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>head</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'head', 'label': 'head', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>head</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'neck',_'label':_'neck',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'neck', 'label': 'neck', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>neck</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'back',_'label':_'back',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'back', 'label': 'back', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>back</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'arms',_'label':_'arms',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>arms</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'arms', 'label': 'arms', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>arms</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'legs',_'label':_'legs',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>legs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'legs', 'label': 'legs', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>legs</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'stomach',_'label':_'stomach',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>stomach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'stomach', 'label': 'stomach', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>stomach</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'hands',_'label':_'hands',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>hands</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'hands', 'label': 'hands', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>hands</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'feet',_'label':_'feet',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>feet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'feet', 'label': 'feet', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>feet</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'excellent',_'label':_'excellent',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'excellent', 'label': 'excellent', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>excellent</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'good',_'label':_'good',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'good', 'label': 'good', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'fair',_'label':_'fair',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'fair', 'label': 'fair', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>fair</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'bad',_'label':_'bad',_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'bad', 'label': 'bad', 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>bad</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_true,_'label':_true,_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': True, 'label': True, 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_false,_'label':_false,_'hint':_none,_'type':_'object',_'options':_[]}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': False, 'label': False, 'hint': None, 'type': 'object', 'options': []}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
